--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/08_BIBS_UXScreens_BRD-01_New_Business_v2.1.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/08_BIBS_UXScreens_BRD-01_New_Business_v2.1.xlsx
@@ -11049,7 +11049,7 @@
       </c>
       <c r="K160" s="45" t="inlineStr">
         <is>
-          <t>CLPC billing file: first page as generated</t>
+          <t>CLPC billing file: first page as generated, with six of its nine columns</t>
         </is>
       </c>
       <c r="L160" s="45" t="inlineStr">
